--- a/data/Ferreterias-CABA-Uniproveedores.xlsx
+++ b/data/Ferreterias-CABA-Uniproveedores.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Seguidores por Red" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ferreterías CABA'!$A$3:$O$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ferreterías CABA'!$A$3:$O$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31,10 +31,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="15"/>
     </font>
     <font>
       <i val="1"/>
@@ -42,7 +41,6 @@
       <sz val="9"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="000D0D0D"/>
       <sz val="11"/>
@@ -71,7 +69,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -90,7 +88,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7F7F7"/>
+        <fgColor rgb="00E9F6C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F6F6E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -120,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -131,27 +139,36 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -525,37 +542,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="34" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>UNIPROVEEDORES · Prospección de Ferreterías — Capital Federal (CABA)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
+          <t>UNIPROVEEDORES · Ferreterías CABA — ordenadas por cercanía al depósito (Bacacay 4726, Comuna 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Datos de directorios públicos (jul-2026). Campos vacíos = completar en la llamada/visita. Actualizá 'Estado' a medida que contactás. WhatsApp marcado 'confirmar' = validar antes de escribir.</t>
+          <t>Anillo 1 = Comuna 10 e inmediato (~0-2 km). Anillo 2 = ~2-6 km. Anillo 3 = resto de CABA. Empezá por Anillo 1 (verde). Campos vacíos = completar en el contacto (ver hoja 'Cómo completar y escalar'). Para bajar TODAS las de Google Maps automáticamente: scripts/scrape_ferreterias_gmaps.py</t>
         </is>
       </c>
     </row>
@@ -567,47 +584,47 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>Anillo</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Barrio</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Dirección</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Teléfono</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>Sitio web / Tienda</t>
-        </is>
-      </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>Sitio web / Redes</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>Instagram</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Facebook</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -642,42 +659,38 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Ferretería del Once</t>
+          <t>Anillo 1</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Balvanera / Once</t>
+          <t>Ferretería (Belaústegui)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Sarmiento 2846</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>011 4687-0696</t>
+          <t>Dr. Luis Belaústegui 3901</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
+          <t>011 4639-0060</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>facebook.com/p/Ferreteria-del-once</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>L-V 9-18, Sáb AM</t>
-        </is>
-      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr"/>
       <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr">
         <is>
@@ -691,54 +704,62 @@
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>35+ años. Zona mayorista Once.</t>
+          <t>Muy cerca del depósito.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>RIVAFER</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Once / Balvanera</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>s/d (consultar web)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>rivafer.com.ar</t>
-        </is>
-      </c>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr"/>
-      <c r="K5" s="7" t="inlineStr"/>
-      <c r="L5" s="7" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Anillo 1</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Ferretería (Yerbal)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Yerbal 3920</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>011 4672-2218</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
-        <is>
-          <t>Tiene e-commerce propio.</t>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Muy cerca del depósito.</t>
         </is>
       </c>
     </row>
@@ -748,27 +769,35 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Ferretería El Once</t>
+          <t>Anillo 1</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Once / Balvanera</t>
+          <t>Ferretería (Gaona 4277)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>s/d (tienda online)</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>ferreteriaelonce.com</t>
-        </is>
-      </c>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Av. Gaona 4277</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>011 4671-7132</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr"/>
       <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
@@ -785,62 +814,62 @@
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>Vende online, buen prospecto mayorista.</t>
+          <t>Sobre avenida, buen tránsito.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>MAABA Distribuidora</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Villa Lugano</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Zelada 6523 (CP 1440)</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>011 7569-4425</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>11 5429-1284</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>maaba.com.ar</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Anillo 1</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Ferretería (J. V. González)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Joaquín V. González 19</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>011 4674-6435</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr"/>
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="O7" s="7" t="inlineStr">
-        <is>
-          <t>Distribuidora de ferretería. Móvil = WhatsApp probable.</t>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>Muy cerca del depósito.</t>
         </is>
       </c>
     </row>
@@ -850,32 +879,36 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Ferretería Belgrano</t>
+          <t>Anillo 1</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Ferretería (Lacarra 53)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Manuel Ugarte 2391 / Zapiola 2468</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
+          <t>Vélez Sarsfield</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Av. Lacarra 53</t>
+        </is>
+      </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
+          <t>011 4674-1101</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>instagram.com/ferreteriabelgrano2</t>
-        </is>
-      </c>
+      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="5" t="inlineStr"/>
       <c r="L8" s="5" t="inlineStr"/>
@@ -891,58 +924,62 @@
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>2 sucursales. Tiene IG activo.</t>
+          <t>Barrio del depósito.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>Ferretería (Monroe)</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Belgrano</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>Av. Monroe 3626</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>011 4541-6047</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="O9" s="7" t="inlineStr">
-        <is>
-          <t>Directorio Belgrano.</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Anillo 1</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Ferretería (E. de San Martín)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>E. de San Martín 4944</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>011 4674-0327</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr"/>
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>Barrio del depósito.</t>
         </is>
       </c>
     </row>
@@ -952,30 +989,34 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Ferretería (Juramento)</t>
+          <t>Anillo 1</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Ferretería (Rivadavia 9825)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Juramento 3125</t>
+          <t>Villa Luro</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>011 4544-9991</t>
+          <t>Av. Rivadavia 9825</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
+          <t>011 4682-1993</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H10" s="5" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr"/>
@@ -988,63 +1029,67 @@
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>Directorio Belgrano.</t>
+          <t>Sobre Rivadavia.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Ferretería (Amenábar)</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Belgrano</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Amenábar 2273</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>011 4787-6355</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr"/>
-      <c r="K11" s="7" t="inlineStr"/>
-      <c r="L11" s="7" t="inlineStr"/>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr">
-        <is>
-          <t>Directorio Belgrano.</t>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Anillo 1</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Ferretería (Víctor Hugo)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Villa Luro</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Víctor Hugo 43</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>011 4682-8050</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Cerca del depósito.</t>
         </is>
       </c>
     </row>
@@ -1054,30 +1099,34 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Ferretería (Blanco Encalada)</t>
+          <t>Anillo 1</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Belgrano</t>
+          <t>Ferretería (Larrañaga)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Blanco Encalada 2606</t>
+          <t>Villa Luro</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>011 4787-4432</t>
+          <t>D. Larrañaga 694</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
+          <t>011 4683-1181</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H12" s="5" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr"/>
       <c r="J12" s="5" t="inlineStr"/>
@@ -1095,58 +1144,62 @@
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
-          <t>Directorio Belgrano.</t>
+          <t>Cerca del depósito.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n">
+      <c r="A13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Ferretería (Moldes)</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Belgrano</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Moldes 1802</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>011 4787-4316</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr"/>
-      <c r="J13" s="7" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="O13" s="7" t="inlineStr">
-        <is>
-          <t>Directorio Belgrano.</t>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Anillo 1</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Ferretería (Álvarez Jonte 4663)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Monte Castro</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Av. Álvarez Jonte 4663</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>011 4567-7997</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>Sobre avenida.</t>
         </is>
       </c>
     </row>
@@ -1156,26 +1209,30 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Ferretería (Palermo)</t>
+          <t>Anillo 1</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Ferretería (Benito Juárez)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Jorge Luis Borges 2475 Local 37</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
+          <t>Monte Castro</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Benito Juárez 1855</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="5" t="inlineStr"/>
@@ -1193,54 +1250,62 @@
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>Directorio Palermo.</t>
+          <t>Directorio Monte Castro.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Mundo Soluciones Caballito</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Caballito</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>P. Lozano 3150</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr"/>
-      <c r="J15" s="7" t="inlineStr"/>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr"/>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Anillo 1</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Ferretería (Lope de Vega 2240)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Villa Real</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Av. Lope de Vega 2240</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>011 4568-8186</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="O15" s="7" t="inlineStr">
-        <is>
-          <t>Directorio Caballito.</t>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
+          <t>Sobre avenida.</t>
         </is>
       </c>
     </row>
@@ -1250,38 +1315,38 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Ferretería y Cerraj. 24hs Trenque</t>
+          <t>Anillo 1</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Villa Urquiza</t>
+          <t>Ferretería (Lope de Vega 2832)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Echeverría 5099 (y Ávalos)</t>
+          <t>Villa Real</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>011 4521-9377</t>
+          <t>Av. Lope de Vega 2832</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>11 5002-4497</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
+          <t>011 4568-8402</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H16" s="5" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>24 hs</t>
-        </is>
-      </c>
+      <c r="K16" s="5" t="inlineStr"/>
       <c r="L16" s="5" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr">
         <is>
@@ -1290,63 +1355,67 @@
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>Sobre avenida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Anillo 1</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Ferretería (Nazca 1311)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Villa Santa Rita</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Av. Nazca 1311</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>011 4584-2809</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>24hs. Móvil = WhatsApp probable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Ferretería (Lavoisier)</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Villa Urquiza</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>Lavoisier 3273</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>011 4573-2278</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr"/>
-      <c r="J17" s="7" t="inlineStr"/>
-      <c r="K17" s="7" t="inlineStr"/>
-      <c r="L17" s="7" t="inlineStr"/>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="O17" s="7" t="inlineStr">
-        <is>
-          <t>Directorio V. Urquiza.</t>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
+          <t>Sobre Nazca (avenida clave).</t>
         </is>
       </c>
     </row>
@@ -1356,30 +1425,34 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Ferretería (Burela)</t>
+          <t>Anillo 1</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Villa Urquiza</t>
+          <t>Ferretería (Nazca 1826)</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Burela 2725</t>
+          <t>Villa Santa Rita</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>011 4521-4337</t>
+          <t>Av. Nazca 1826</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
+          <t>011 4584-6513</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H18" s="5" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="5" t="inlineStr"/>
@@ -1392,63 +1465,63 @@
       </c>
       <c r="N18" s="5" t="inlineStr">
         <is>
-          <t>Media</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>Directorio V. Urquiza.</t>
+          <t>Sobre Nazca.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n">
+      <c r="A19" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Ferretería (Bauness)</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Villa Urquiza</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>Bauness 2201</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>011 4521-9229</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
-      <c r="J19" s="7" t="inlineStr"/>
-      <c r="K19" s="7" t="inlineStr"/>
-      <c r="L19" s="7" t="inlineStr"/>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="O19" s="7" t="inlineStr">
-        <is>
-          <t>Directorio V. Urquiza.</t>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Anillo 1</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Materiales Cardinale S.R.L.</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Villa del Parque</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Av. Mosconi 3992</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
+          <t>Materiales + ferretería. Volumen.</t>
         </is>
       </c>
     </row>
@@ -1458,30 +1531,30 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Ferretería (Monroe 3897)</t>
+          <t>Anillo 1</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Villa Urquiza</t>
+          <t>Ferretería del Parque</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Av. Monroe 3897</t>
+          <t>Villa del Parque</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>011 4545-4829</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
+          <t>(consultar - Páginas Amarillas)</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H20" s="5" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="5" t="inlineStr"/>
@@ -1499,54 +1572,62 @@
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>Directorio V. Urquiza.</t>
+          <t>Ficha PáginasAmarillas.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n">
+      <c r="A21" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Ferretería Del Norte</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>Villa Urquiza</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>s/d (Buscabaires)</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr"/>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
-      <c r="J21" s="7" t="inlineStr"/>
-      <c r="K21" s="7" t="inlineStr"/>
-      <c r="L21" s="7" t="inlineStr"/>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="O21" s="7" t="inlineStr">
-        <is>
-          <t>Ficha Buscabaires — verificar dirección.</t>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Anillo 1</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Ferretería (Nazarre)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Villa del Parque</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Nazarre 3256</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>011 4587-6243</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
+          <t>Directorio V. del Parque.</t>
         </is>
       </c>
     </row>
@@ -1556,26 +1637,30 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Ferretería JS</t>
+          <t>Anillo 1</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Villa Urquiza</t>
+          <t>Herramientas Dali S.R.L.</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>s/d (Buscabaires)</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
+          <t>Villa del Parque</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Av. Juan B. Justo 5768</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H22" s="5" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="5" t="inlineStr"/>
@@ -1588,12 +1673,12 @@
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>Ficha Buscabaires — verificar dirección.</t>
+          <t>Herramientas. Posible mayorista.</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1688,36 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Argentec Herramientas (Boedo)</t>
+          <t>Anillo 2</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Boedo</t>
+          <t>Ferretería Santa María</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Av. Asamblea 524</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>argentec.com.ar</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="inlineStr"/>
+          <t>Caballito</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>Av. La Plata 213</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>ferreteriasantamaria.com.ar</t>
+        </is>
+      </c>
       <c r="J23" s="7" t="inlineStr"/>
       <c r="K23" s="7" t="inlineStr"/>
       <c r="L23" s="7" t="inlineStr"/>
@@ -1644,58 +1733,62 @@
       </c>
       <c r="O23" s="7" t="inlineStr">
         <is>
-          <t>Cadena c/ red de sucursales y web.</t>
+          <t>Web propia. Buen prospecto.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n">
+      <c r="A24" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>Argentec Herramientas (Flores)</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Flores</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Av. Gaona 3059</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>argentec.com.ar</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería Online</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>Caballito</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>Av. Rivadavia 5456 Local 16</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>ferreteriaonline.com.ar</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>Cadena c/ web.</t>
+      <c r="O24" s="7" t="inlineStr">
+        <is>
+          <t>E-commerce de herramientas industriales.</t>
         </is>
       </c>
     </row>
@@ -1705,32 +1798,36 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Argentec Herramientas (V.Crespo)</t>
+          <t>Anillo 2</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>Villa Crespo</t>
+          <t>LB Ferreterías</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>Av. Córdoba 5786</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>argentec.com.ar</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr"/>
+          <t>Caballito</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Av. Honorio Pueyrredón 1182</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>lbferreterias.com.ar</t>
+        </is>
+      </c>
       <c r="J25" s="7" t="inlineStr"/>
       <c r="K25" s="7" t="inlineStr"/>
       <c r="L25" s="7" t="inlineStr"/>
@@ -1746,58 +1843,62 @@
       </c>
       <c r="O25" s="7" t="inlineStr">
         <is>
-          <t>Cadena c/ web.</t>
+          <t>Web propia.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n">
+      <c r="A26" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>Argentec Herramientas (V.Crespo 2)</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Villa Crespo</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Av. Córdoba 4038</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>argentec.com.ar</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="5" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Mercado del Progreso (sector ferret.)</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Caballito</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Av. Rivadavia 5430</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>mercadodelprogreso.com</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>Cadena c/ web.</t>
+      <c r="O26" s="7" t="inlineStr">
+        <is>
+          <t>Puestos de ferretería/electricidad.</t>
         </is>
       </c>
     </row>
@@ -1807,26 +1908,34 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Herramientas Dali S.R.L.</t>
+          <t>Anillo 2</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>Villa Crespo</t>
+          <t>Ferretería (Avellaneda 2287)</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Montenegro 32</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr"/>
+          <t>Flores</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>Av. Avellaneda 2287</t>
+        </is>
+      </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr"/>
+          <t>011 4631-0351</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H27" s="7" t="inlineStr"/>
       <c r="I27" s="7" t="inlineStr"/>
       <c r="J27" s="7" t="inlineStr"/>
@@ -1844,54 +1953,62 @@
       </c>
       <c r="O27" s="7" t="inlineStr">
         <is>
-          <t>Directorio V. Crespo.</t>
+          <t>Sobre avenida comercial.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n">
+      <c r="A28" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>Ferretería (Crisólogo Larralde)</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Núñez</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Crisólogo Larralde 1982</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
-      <c r="L28" s="5" t="inlineStr"/>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería (Directorio 2320)</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Flores</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Av. Directorio 2320</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>011 4634-1301</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr"/>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr"/>
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>Directorio Núñez.</t>
+      <c r="O28" s="7" t="inlineStr">
+        <is>
+          <t>Directorio Flores.</t>
         </is>
       </c>
     </row>
@@ -1901,26 +2018,34 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Ferretería (Pacheco)</t>
+          <t>Anillo 2</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Ferretería (Eva Perón 2951)</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Pacheco 3545</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr"/>
+          <t>Flores</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Av. Eva Perón 2951</t>
+        </is>
+      </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr"/>
+          <t>011 4660-6105</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="7" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr"/>
@@ -1938,54 +2063,62 @@
       </c>
       <c r="O29" s="7" t="inlineStr">
         <is>
-          <t>Directorio Saavedra.</t>
+          <t>Sobre avenida.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n">
+      <c r="A30" s="6" t="n">
         <v>27</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>Ferretería (Ruiz Huidobro)</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Saavedra</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Ruiz Huidobro 2663</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
-      <c r="L30" s="5" t="inlineStr"/>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="O30" s="5" t="inlineStr">
-        <is>
-          <t>Directorio Saavedra.</t>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Argentec Herramientas (Flores)</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Flores</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Av. Gaona 3059</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>argentec.com.ar</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr">
+        <is>
+          <t>Cadena con red de sucursales y web.</t>
         </is>
       </c>
     </row>
@@ -1995,26 +2128,34 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Ferretería (Sanabria)</t>
+          <t>Anillo 2</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>Villa Devoto</t>
+          <t>Ferretería (Eva Perón 4285)</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Sanabria 2885</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr"/>
+          <t>Parque Avellaneda</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Av. Eva Perón 4285</t>
+        </is>
+      </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr"/>
+          <t>011 4671-6241</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H31" s="7" t="inlineStr"/>
       <c r="I31" s="7" t="inlineStr"/>
       <c r="J31" s="7" t="inlineStr"/>
@@ -2032,54 +2173,62 @@
       </c>
       <c r="O31" s="7" t="inlineStr">
         <is>
-          <t>Directorio V. Devoto.</t>
+          <t>Sobre avenida.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n">
+      <c r="A32" s="6" t="n">
         <v>29</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>Ferretería (Segurola)</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Villa Devoto</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>Av. Segurola 2884</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="5" t="inlineStr"/>
-      <c r="L32" s="5" t="inlineStr"/>
-      <c r="M32" s="5" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería (Mariano Acosta)</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>Parque Avellaneda</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>Mariano Acosta 1066</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>011 4613-9083</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr"/>
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>Directorio V. Devoto.</t>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>Directorio Pque Avellaneda.</t>
         </is>
       </c>
     </row>
@@ -2089,26 +2238,34 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Ferretería (Marcos Paz)</t>
+          <t>Anillo 2</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>Villa Devoto</t>
+          <t>Ferretería (Eva Perón 4388)</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Marcos Paz 4510</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr"/>
+          <t>Parque Avellaneda</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>Av. Eva Perón 4388</t>
+        </is>
+      </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr"/>
+          <t>011 4672-1745</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="7" t="inlineStr"/>
       <c r="J33" s="7" t="inlineStr"/>
@@ -2126,54 +2283,62 @@
       </c>
       <c r="O33" s="7" t="inlineStr">
         <is>
-          <t>Directorio V. Devoto.</t>
+          <t>Sobre avenida.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Ferretería Avenida</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Mataderos</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>s/d (Buscabaires)</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="5" t="inlineStr"/>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>Ficha Buscabaires — verificar dirección.</t>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería (Barco Centenera)</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Parque Chacabuco</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>Av. del Barco Centenera 2227</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>011 4923-4098</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr"/>
+      <c r="J34" s="7" t="inlineStr"/>
+      <c r="K34" s="7" t="inlineStr"/>
+      <c r="L34" s="7" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O34" s="7" t="inlineStr">
+        <is>
+          <t>Sobre avenida.</t>
         </is>
       </c>
     </row>
@@ -2183,26 +2348,34 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Ferretería (Alberdi)</t>
+          <t>Anillo 2</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>Mataderos</t>
+          <t>Ferretería (Directorio 1650)</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Av. J.B. Alberdi 5775</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr"/>
+          <t>Parque Chacabuco</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>Av. Directorio 1650</t>
+        </is>
+      </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr"/>
+          <t>011 4432-79 (confirmar)</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="7" t="inlineStr"/>
       <c r="J35" s="7" t="inlineStr"/>
@@ -2220,54 +2393,62 @@
       </c>
       <c r="O35" s="7" t="inlineStr">
         <is>
-          <t>Directorio Mataderos.</t>
+          <t>Verificar teléfono completo.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n">
+      <c r="A36" s="6" t="n">
         <v>33</v>
       </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Ferretería (Larrazábal)</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Mataderos</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Av. Larrazábal 966</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="5" t="inlineStr"/>
-      <c r="L36" s="5" t="inlineStr"/>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería (Donato Álvarez 2203)</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>La Paternal</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>Av. Donato Álvarez 2203</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>011 4826-4009</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr"/>
+      <c r="J36" s="7" t="inlineStr"/>
+      <c r="K36" s="7" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
-        <is>
-          <t>Directorio Mataderos.</t>
+      <c r="O36" s="7" t="inlineStr">
+        <is>
+          <t>Sobre avenida.</t>
         </is>
       </c>
     </row>
@@ -2277,26 +2458,34 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Ferretería (Eva Perón)</t>
+          <t>Anillo 2</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Mataderos</t>
+          <t>Ferretería (Donato Álvarez 3156)</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Av. Eva Perón 5553</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr"/>
+          <t>La Paternal</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>Av. Donato Álvarez 3156</t>
+        </is>
+      </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr"/>
+          <t>011 4521-2682</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="7" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr"/>
@@ -2314,54 +2503,62 @@
       </c>
       <c r="O37" s="7" t="inlineStr">
         <is>
-          <t>Directorio Mataderos.</t>
+          <t>Sobre avenida.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n">
+      <c r="A38" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>Ferretería (Oliden)</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Mataderos</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>Oliden 2150</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr"/>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr"/>
-      <c r="J38" s="5" t="inlineStr"/>
-      <c r="K38" s="5" t="inlineStr"/>
-      <c r="L38" s="5" t="inlineStr"/>
-      <c r="M38" s="5" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería (San Martín 3202)</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>La Paternal</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>Av. San Martín 3202</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>011 4581-6195</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr"/>
+      <c r="J38" s="7" t="inlineStr"/>
+      <c r="K38" s="7" t="inlineStr"/>
+      <c r="L38" s="7" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>Directorio Mataderos.</t>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>Sobre avenida San Martín.</t>
         </is>
       </c>
     </row>
@@ -2371,28 +2568,36 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Ferretería Montiel</t>
+          <t>Anillo 2</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Liniers</t>
+          <t>Argentec Herramientas (V. Crespo)</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>s/d (Infoisinfo)</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr"/>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr"/>
+          <t>Villa Crespo</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>Av. Córdoba 5786</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>argentec.com.ar</t>
+        </is>
+      </c>
       <c r="J39" s="7" t="inlineStr"/>
       <c r="K39" s="7" t="inlineStr"/>
       <c r="L39" s="7" t="inlineStr"/>
@@ -2403,59 +2608,67 @@
       </c>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="O39" s="7" t="inlineStr">
         <is>
-          <t>Verificar dirección.</t>
+          <t>Cadena con web.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n">
+      <c r="A40" s="6" t="n">
         <v>37</v>
       </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Ferretería El Ahorro</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Liniers</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>s/d (Infoisinfo)</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr"/>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr"/>
-      <c r="J40" s="5" t="inlineStr"/>
-      <c r="K40" s="5" t="inlineStr"/>
-      <c r="L40" s="5" t="inlineStr"/>
-      <c r="M40" s="5" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>Verificar dirección.</t>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Argentec Herramientas (V. Crespo 2)</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>Villa Crespo</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Av. Córdoba 4038</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>argentec.com.ar</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>Cadena con web.</t>
         </is>
       </c>
     </row>
@@ -2465,37 +2678,33 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Ferretería San Telmo S.R.L.</t>
+          <t>Anillo 2</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Herramientas Dali S.R.L. (V. Crespo)</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>s/d (consultar IG/FB)</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr"/>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr"/>
+          <t>Villa Crespo</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Montenegro 32</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr">
-        <is>
-          <t>instagram.com/ferreteriasantelmo</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="inlineStr">
-        <is>
-          <t>facebook.com/p/FERRETERIA-SAN-TELMO-SRL</t>
-        </is>
-      </c>
+      <c r="I41" s="7" t="inlineStr"/>
+      <c r="J41" s="7" t="inlineStr"/>
       <c r="K41" s="7" t="inlineStr"/>
       <c r="L41" s="7" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr">
@@ -2505,63 +2714,67 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>Directorio V. Crespo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Argentec Herramientas (Boedo)</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>Boedo</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Av. Asamblea 524</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr"/>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>argentec.com.ar</t>
+        </is>
+      </c>
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="O41" s="7" t="inlineStr">
-        <is>
-          <t>IG + FB activos. Buen prospecto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="n">
-        <v>39</v>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>Ferretería (Defensa)</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>San Telmo</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Defensa 732</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>011 4362-3299</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="5" t="inlineStr"/>
-      <c r="L42" s="5" t="inlineStr"/>
-      <c r="M42" s="5" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N42" s="5" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>Directorio San Telmo.</t>
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>Cadena con web.</t>
         </is>
       </c>
     </row>
@@ -2571,30 +2784,34 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Ferretería (Av. Brasil)</t>
+          <t>Anillo 2</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Casa Aldo (ferretería y herrajes)</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Av. Brasil 601</t>
+          <t>Villa Pueyrredón</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>011 4300-7763</t>
+          <t>Salvador M. del Carril 2921</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr"/>
+          <t>011 4572-7412</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="7" t="inlineStr"/>
       <c r="J43" s="7" t="inlineStr"/>
@@ -2612,58 +2829,62 @@
       </c>
       <c r="O43" s="7" t="inlineStr">
         <is>
-          <t>Directorio zona sur.</t>
+          <t>Ferretería + herrajes.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n">
+      <c r="A44" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>Ferretería (Chacabuco)</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>San Telmo</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Chacabuco 798</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>011 4300-6970</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="5" t="inlineStr"/>
-      <c r="L44" s="5" t="inlineStr"/>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="O44" s="5" t="inlineStr">
-        <is>
-          <t>Directorio San Telmo.</t>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería (Artigas 5676)</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>Villa Pueyrredón</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>Gral. Artigas 5676</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>011 4572-7616</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr"/>
+      <c r="J44" s="7" t="inlineStr"/>
+      <c r="K44" s="7" t="inlineStr"/>
+      <c r="L44" s="7" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>Directorio V. Pueyrredón.</t>
         </is>
       </c>
     </row>
@@ -2673,30 +2894,34 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Ferretería (San Antonio)</t>
+          <t>Anillo 2</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Barracas</t>
+          <t>Ferretería (Artigas 5299)</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>San Antonio 440</t>
+          <t>Villa Pueyrredón</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>011 4302-6979</t>
+          <t>Gral. Artigas 5299</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr"/>
+          <t>011 4571-2586</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H45" s="7" t="inlineStr"/>
       <c r="I45" s="7" t="inlineStr"/>
       <c r="J45" s="7" t="inlineStr"/>
@@ -2709,63 +2934,63 @@
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>Directorio V. Pueyrredón.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería (Alberdi 5775)</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>Mataderos</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Av. J.B. Alberdi 5775</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr"/>
+      <c r="I46" s="7" t="inlineStr"/>
+      <c r="J46" s="7" t="inlineStr"/>
+      <c r="K46" s="7" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="O45" s="7" t="inlineStr">
-        <is>
-          <t>Directorio Barracas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>43</v>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Ferretería (Salom)</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Barracas</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Salom 326</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>011 4302-5832</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr"/>
-      <c r="L46" s="5" t="inlineStr"/>
-      <c r="M46" s="5" t="inlineStr">
-        <is>
-          <t>Sin contactar</t>
-        </is>
-      </c>
-      <c r="N46" s="5" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t>Directorio Barracas.</t>
+      <c r="O46" s="7" t="inlineStr">
+        <is>
+          <t>Sobre avenida.</t>
         </is>
       </c>
     </row>
@@ -2775,30 +3000,30 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Ferretería (Rocha)</t>
+          <t>Anillo 2</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Barracas</t>
+          <t>Ferretería (Larrazábal)</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Rocha 1600</t>
+          <t>Mataderos</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>011 4302-5122</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>confirmar</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr"/>
+          <t>Av. Larrazábal 966</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
       <c r="H47" s="7" t="inlineStr"/>
       <c r="I47" s="7" t="inlineStr"/>
       <c r="J47" s="7" t="inlineStr"/>
@@ -2816,12 +3041,1846 @@
       </c>
       <c r="O47" s="7" t="inlineStr">
         <is>
+          <t>Sobre avenida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería (Eva Perón 5553)</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>Mataderos</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Av. Eva Perón 5553</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr"/>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr"/>
+      <c r="J48" s="7" t="inlineStr"/>
+      <c r="K48" s="7" t="inlineStr"/>
+      <c r="L48" s="7" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O48" s="7" t="inlineStr">
+        <is>
+          <t>Sobre avenida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería (Oliden)</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>Mataderos</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>Oliden 2150</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr"/>
+      <c r="J49" s="7" t="inlineStr"/>
+      <c r="K49" s="7" t="inlineStr"/>
+      <c r="L49" s="7" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="O49" s="7" t="inlineStr">
+        <is>
+          <t>Directorio Mataderos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería Avenida</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>Mataderos</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>(consultar - Buscabaires)</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr"/>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr"/>
+      <c r="J50" s="7" t="inlineStr"/>
+      <c r="K50" s="7" t="inlineStr"/>
+      <c r="L50" s="7" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="O50" s="7" t="inlineStr">
+        <is>
+          <t>Verificar dirección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería Montiel</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>Liniers</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>(consultar - Infoisinfo)</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr"/>
+      <c r="J51" s="7" t="inlineStr"/>
+      <c r="K51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="O51" s="7" t="inlineStr">
+        <is>
+          <t>Verificar dirección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería El Ahorro</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>Liniers</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>(consultar - Infoisinfo)</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr"/>
+      <c r="J52" s="7" t="inlineStr"/>
+      <c r="K52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="O52" s="7" t="inlineStr">
+        <is>
+          <t>Verificar dirección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería (Sanabria)</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>Villa Devoto</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>Sanabria 2885</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr"/>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr"/>
+      <c r="J53" s="7" t="inlineStr"/>
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O53" s="7" t="inlineStr">
+        <is>
+          <t>Directorio V. Devoto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería (Segurola)</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>Villa Devoto</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>Av. Segurola 2884</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr"/>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr"/>
+      <c r="J54" s="7" t="inlineStr"/>
+      <c r="K54" s="7" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O54" s="7" t="inlineStr">
+        <is>
+          <t>Sobre avenida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Ferretería (Marcos Paz)</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>Villa Devoto</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Marcos Paz 4510</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr"/>
+      <c r="J55" s="7" t="inlineStr"/>
+      <c r="K55" s="7" t="inlineStr"/>
+      <c r="L55" s="7" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="inlineStr">
+        <is>
+          <t>Directorio V. Devoto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería del Once</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>Balvanera / Once</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>Sarmiento 2846</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>011 4687-0696</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr"/>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>facebook.com/p/Ferreteria-del-once</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr"/>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>L-V 9-18, Sáb AM</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr"/>
+      <c r="M56" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N56" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O56" s="9" t="inlineStr">
+        <is>
+          <t>Zona mayorista Once. 35+ años.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>RIVAFER</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>Once / Balvanera</t>
+        </is>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>(consultar web)</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr"/>
+      <c r="G57" s="9" t="inlineStr"/>
+      <c r="H57" s="9" t="inlineStr"/>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>rivafer.com.ar</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="inlineStr"/>
+      <c r="K57" s="9" t="inlineStr"/>
+      <c r="L57" s="9" t="inlineStr"/>
+      <c r="M57" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N57" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O57" s="9" t="inlineStr">
+        <is>
+          <t>E-commerce propio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería El Once</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>Once / Balvanera</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>(tienda online)</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr"/>
+      <c r="G58" s="9" t="inlineStr"/>
+      <c r="H58" s="9" t="inlineStr"/>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>ferreteriaelonce.com</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="inlineStr"/>
+      <c r="K58" s="9" t="inlineStr"/>
+      <c r="L58" s="9" t="inlineStr"/>
+      <c r="M58" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N58" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O58" s="9" t="inlineStr">
+        <is>
+          <t>Vende online. Mayorista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>MAABA Distribuidora</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>Villa Lugano</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>Zelada 6523</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>011 7569-4425</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>11 5429-1284</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr"/>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>maaba.com.ar</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr"/>
+      <c r="K59" s="9" t="inlineStr"/>
+      <c r="L59" s="9" t="inlineStr"/>
+      <c r="M59" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N59" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O59" s="9" t="inlineStr">
+        <is>
+          <t>Distribuidora. Móvil = WhatsApp probable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería Belgrano</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>Manuel Ugarte 2391 / Zapiola 2468</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr"/>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H60" s="9" t="inlineStr"/>
+      <c r="I60" s="9" t="inlineStr"/>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>instagram.com/ferreteriabelgrano2</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr"/>
+      <c r="L60" s="9" t="inlineStr"/>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O60" s="9" t="inlineStr">
+        <is>
+          <t>2 sucursales. IG activo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Monroe 3626)</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>Av. Monroe 3626</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>011 4541-6047</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H61" s="9" t="inlineStr"/>
+      <c r="I61" s="9" t="inlineStr"/>
+      <c r="J61" s="9" t="inlineStr"/>
+      <c r="K61" s="9" t="inlineStr"/>
+      <c r="L61" s="9" t="inlineStr"/>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O61" s="9" t="inlineStr">
+        <is>
+          <t>Directorio Belgrano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Juramento)</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>Juramento 3125</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>011 4544-9991</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H62" s="9" t="inlineStr"/>
+      <c r="I62" s="9" t="inlineStr"/>
+      <c r="J62" s="9" t="inlineStr"/>
+      <c r="K62" s="9" t="inlineStr"/>
+      <c r="L62" s="9" t="inlineStr"/>
+      <c r="M62" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N62" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O62" s="9" t="inlineStr">
+        <is>
+          <t>Directorio Belgrano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Amenábar)</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>Amenábar 2273</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>011 4787-6355</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H63" s="9" t="inlineStr"/>
+      <c r="I63" s="9" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr"/>
+      <c r="K63" s="9" t="inlineStr"/>
+      <c r="L63" s="9" t="inlineStr"/>
+      <c r="M63" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N63" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O63" s="9" t="inlineStr">
+        <is>
+          <t>Directorio Belgrano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Blanco Encalada)</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>Blanco Encalada 2606</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>011 4787-4432</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H64" s="9" t="inlineStr"/>
+      <c r="I64" s="9" t="inlineStr"/>
+      <c r="J64" s="9" t="inlineStr"/>
+      <c r="K64" s="9" t="inlineStr"/>
+      <c r="L64" s="9" t="inlineStr"/>
+      <c r="M64" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N64" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O64" s="9" t="inlineStr">
+        <is>
+          <t>Directorio Belgrano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Moldes)</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Belgrano</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>Moldes 1802</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>011 4787-4316</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H65" s="9" t="inlineStr"/>
+      <c r="I65" s="9" t="inlineStr"/>
+      <c r="J65" s="9" t="inlineStr"/>
+      <c r="K65" s="9" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr"/>
+      <c r="M65" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N65" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O65" s="9" t="inlineStr">
+        <is>
+          <t>Directorio Belgrano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería y Cerraj. 24hs Trenque</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Villa Urquiza</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>Echeverría 5099 (y Ávalos)</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>011 4521-9377</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>11 5002-4497</t>
+        </is>
+      </c>
+      <c r="H66" s="9" t="inlineStr"/>
+      <c r="I66" s="9" t="inlineStr"/>
+      <c r="J66" s="9" t="inlineStr"/>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>24 hs</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr"/>
+      <c r="M66" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N66" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O66" s="9" t="inlineStr">
+        <is>
+          <t>24hs. Móvil = WhatsApp probable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Lavoisier)</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Villa Urquiza</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>Lavoisier 3273</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>011 4573-2278</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H67" s="9" t="inlineStr"/>
+      <c r="I67" s="9" t="inlineStr"/>
+      <c r="J67" s="9" t="inlineStr"/>
+      <c r="K67" s="9" t="inlineStr"/>
+      <c r="L67" s="9" t="inlineStr"/>
+      <c r="M67" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N67" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O67" s="9" t="inlineStr">
+        <is>
+          <t>Directorio V. Urquiza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Burela)</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>Villa Urquiza</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>Burela 2725</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>011 4521-4337</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H68" s="9" t="inlineStr"/>
+      <c r="I68" s="9" t="inlineStr"/>
+      <c r="J68" s="9" t="inlineStr"/>
+      <c r="K68" s="9" t="inlineStr"/>
+      <c r="L68" s="9" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O68" s="9" t="inlineStr">
+        <is>
+          <t>Directorio V. Urquiza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Bauness)</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Villa Urquiza</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>Bauness 2201</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>011 4521-9229</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H69" s="9" t="inlineStr"/>
+      <c r="I69" s="9" t="inlineStr"/>
+      <c r="J69" s="9" t="inlineStr"/>
+      <c r="K69" s="9" t="inlineStr"/>
+      <c r="L69" s="9" t="inlineStr"/>
+      <c r="M69" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N69" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O69" s="9" t="inlineStr">
+        <is>
+          <t>Directorio V. Urquiza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Monroe 3897)</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Villa Urquiza</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>Av. Monroe 3897</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>011 4545-4829</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="inlineStr"/>
+      <c r="I70" s="9" t="inlineStr"/>
+      <c r="J70" s="9" t="inlineStr"/>
+      <c r="K70" s="9" t="inlineStr"/>
+      <c r="L70" s="9" t="inlineStr"/>
+      <c r="M70" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N70" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O70" s="9" t="inlineStr">
+        <is>
+          <t>Directorio V. Urquiza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Palermo)</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>Jorge Luis Borges 2475 Local 37</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr"/>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr"/>
+      <c r="I71" s="9" t="inlineStr"/>
+      <c r="J71" s="9" t="inlineStr"/>
+      <c r="K71" s="9" t="inlineStr"/>
+      <c r="L71" s="9" t="inlineStr"/>
+      <c r="M71" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N71" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O71" s="9" t="inlineStr">
+        <is>
+          <t>Directorio Palermo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Crisólogo Larralde)</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Núñez</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>Crisólogo Larralde 1982</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr"/>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H72" s="9" t="inlineStr"/>
+      <c r="I72" s="9" t="inlineStr"/>
+      <c r="J72" s="9" t="inlineStr"/>
+      <c r="K72" s="9" t="inlineStr"/>
+      <c r="L72" s="9" t="inlineStr"/>
+      <c r="M72" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N72" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O72" s="9" t="inlineStr">
+        <is>
+          <t>Directorio Núñez.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Pacheco)</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>Pacheco 3545</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H73" s="9" t="inlineStr"/>
+      <c r="I73" s="9" t="inlineStr"/>
+      <c r="J73" s="9" t="inlineStr"/>
+      <c r="K73" s="9" t="inlineStr"/>
+      <c r="L73" s="9" t="inlineStr"/>
+      <c r="M73" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N73" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O73" s="9" t="inlineStr">
+        <is>
+          <t>Directorio Saavedra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Ruiz Huidobro)</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>Ruiz Huidobro 2663</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr"/>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H74" s="9" t="inlineStr"/>
+      <c r="I74" s="9" t="inlineStr"/>
+      <c r="J74" s="9" t="inlineStr"/>
+      <c r="K74" s="9" t="inlineStr"/>
+      <c r="L74" s="9" t="inlineStr"/>
+      <c r="M74" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N74" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O74" s="9" t="inlineStr">
+        <is>
+          <t>Directorio Saavedra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería San Telmo S.R.L.</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr">
+        <is>
+          <t>(consultar IG/FB)</t>
+        </is>
+      </c>
+      <c r="F75" s="9" t="inlineStr"/>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H75" s="9" t="inlineStr"/>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>facebook.com/p/FERRETERIA-SAN-TELMO-SRL</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="inlineStr">
+        <is>
+          <t>instagram.com/ferreteriasantelmo</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="inlineStr"/>
+      <c r="L75" s="9" t="inlineStr"/>
+      <c r="M75" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N75" s="9" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="O75" s="9" t="inlineStr">
+        <is>
+          <t>IG + FB activos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Defensa)</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="inlineStr">
+        <is>
+          <t>Defensa 732</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>011 4362-3299</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H76" s="9" t="inlineStr"/>
+      <c r="I76" s="9" t="inlineStr"/>
+      <c r="J76" s="9" t="inlineStr"/>
+      <c r="K76" s="9" t="inlineStr"/>
+      <c r="L76" s="9" t="inlineStr"/>
+      <c r="M76" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N76" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O76" s="9" t="inlineStr">
+        <is>
+          <t>Directorio San Telmo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Av. Brasil)</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>Av. Brasil 601</t>
+        </is>
+      </c>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>011 4300-7763</t>
+        </is>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H77" s="9" t="inlineStr"/>
+      <c r="I77" s="9" t="inlineStr"/>
+      <c r="J77" s="9" t="inlineStr"/>
+      <c r="K77" s="9" t="inlineStr"/>
+      <c r="L77" s="9" t="inlineStr"/>
+      <c r="M77" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N77" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O77" s="9" t="inlineStr">
+        <is>
+          <t>Zona sur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Chacabuco)</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>Chacabuco 798</t>
+        </is>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>011 4300-6970</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H78" s="9" t="inlineStr"/>
+      <c r="I78" s="9" t="inlineStr"/>
+      <c r="J78" s="9" t="inlineStr"/>
+      <c r="K78" s="9" t="inlineStr"/>
+      <c r="L78" s="9" t="inlineStr"/>
+      <c r="M78" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N78" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O78" s="9" t="inlineStr">
+        <is>
+          <t>Directorio San Telmo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (San Antonio)</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>Barracas</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>San Antonio 440</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>011 4302-6979</t>
+        </is>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H79" s="9" t="inlineStr"/>
+      <c r="I79" s="9" t="inlineStr"/>
+      <c r="J79" s="9" t="inlineStr"/>
+      <c r="K79" s="9" t="inlineStr"/>
+      <c r="L79" s="9" t="inlineStr"/>
+      <c r="M79" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N79" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O79" s="9" t="inlineStr">
+        <is>
           <t>Directorio Barracas.</t>
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Salom)</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>Barracas</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="inlineStr">
+        <is>
+          <t>Salom 326</t>
+        </is>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>011 4302-5832</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H80" s="9" t="inlineStr"/>
+      <c r="I80" s="9" t="inlineStr"/>
+      <c r="J80" s="9" t="inlineStr"/>
+      <c r="K80" s="9" t="inlineStr"/>
+      <c r="L80" s="9" t="inlineStr"/>
+      <c r="M80" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N80" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O80" s="9" t="inlineStr">
+        <is>
+          <t>Directorio Barracas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="9" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>Ferretería (Rocha)</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>Barracas</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
+        <is>
+          <t>Rocha 1600</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>011 4302-5122</t>
+        </is>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>confirmar</t>
+        </is>
+      </c>
+      <c r="H81" s="9" t="inlineStr"/>
+      <c r="I81" s="9" t="inlineStr"/>
+      <c r="J81" s="9" t="inlineStr"/>
+      <c r="K81" s="9" t="inlineStr"/>
+      <c r="L81" s="9" t="inlineStr"/>
+      <c r="M81" s="9" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="N81" s="9" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="O81" s="9" t="inlineStr">
+        <is>
+          <t>Directorio Barracas.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:O47"/>
+  <autoFilter ref="A3:O81"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
@@ -2839,173 +4898,165 @@
   <dimension ref="B1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="112" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cómo completar los datos que faltan (y encontrar ferreterías nuevas)</t>
+    <row r="1" ht="24" customHeight="1">
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cómo completar datos que faltan y llegar a TODA CABA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="9" t="inlineStr"/>
+      <c r="B2" s="11" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  A) Completar Encargado / Email / WhatsApp / Horario de cada ficha</t>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Realidad del número</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>Estos datos casi nunca están en directorios. Se consiguen así, en orden de rapidez:</t>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>No hay padrón público de ferreterías de CABA. Estimación realista: entre ~800 y ~1.500 ferreterías en toda la Ciudad (no 10.000: ese número sería para toda la Argentina). Igual son MUCHÍSIMAS más de las que podés cargar a mano → por eso está el script.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>1) Google Maps (la mejor fuente y gratis)</t>
-        </is>
-      </c>
+      <c r="B5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Buscá el nombre + dirección en maps.google.com. La ficha del negocio muestra teléfono, sitio web, horarios reales y a veces WhatsApp.</t>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  A) Bajar TODAS automáticamente (Google Maps) — recomendado</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • El botón 'Sitio web' suele llevar a su IG/Facebook/tienda → de ahí sacás redes y WhatsApp.</t>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   scripts/scrape_ferreterias_gmaps.py  (ver instrucciones dentro del archivo)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>2) WhatsApp Business (para validar el número)</t>
+          <t xml:space="preserve">   • Centra la búsqueda en el depósito (Bacacay 4726) y trae cada ferretería con nombre, dirección, teléfono, web,</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Guardá el teléfono y abrí wa.me/54911XXXXXXXX. Si tiene foto/estado de empresa, es WhatsApp válido → marcá la celda en verde.</t>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     horario y rating, ordenadas por distancia. Exporta un Excel igual a este.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>3) El nombre del encargado se pide en el primer contacto</t>
+          <t xml:space="preserve">   • Necesita una API key de Google Maps (Places API) — gratis hasta un límite mensual alto. Pasos en el script.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Por teléfono/WhatsApp: '¿Con quién tengo el gusto? ¿Quién hace las compras?'. Se anota en la columna Encargado. NO se inventa.</t>
-        </is>
-      </c>
+      <c r="B11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="B12" s="9" t="inlineStr"/>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  B) Completar Encargado / Email / WhatsApp / Horario de cada ficha</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B) Encontrar ferreterías NUEVAS cada semana (fuentes)</t>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1) Google Maps: la ficha da teléfono, web, horarios reales y link a IG/WhatsApp.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>Rotá una zona/fuente por semana para no repetir y llegar a toda CABA:</t>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2) WhatsApp Business: abrí wa.me/54911XXXXXXXX; si tiene perfil de empresa, es WhatsApp válido → pintá la celda de verde.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Google Maps: buscá 'ferretería' + barrio, movés el mapa y agregás las que no estén en la lista. (CABA tiene cientos.)</t>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   3) El nombre del encargado se PREGUNTA en el primer contacto ('¿quién hace las compras?'). No se inventa.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Directorios: guiaferreterias.com.ar/capital-federal, paginasamarillas.com.ar, argentino.com.ar, buscabaires.com (filtran por barrio).</t>
-        </is>
-      </c>
+      <c r="B16" s="11" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Instagram/Facebook: buscar 'ferretería + barrio'; muchas PyMEs solo están en redes.</t>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  C) Encontrar ferreterías NUEVAS cada semana</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Mercado Libre: vendedores del rubro ferretería/herramientas en CABA = posibles revendedores.</t>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Google Maps: 'ferretería + barrio', mové el mapa y sumá las que falten.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Grupos/cámaras: CAFARA (Cámara Argentina de Ferreterías) y grupos de compra del rubro.</t>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Directorios: guiaferreterias.com.ar, paginasamarillas.com.ar, argentino.com.ar, buscabaires.com, licuo.com.ar (por barrio).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="9" t="inlineStr"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Instagram/Facebook: 'ferretería + barrio' (muchas PyMEs solo están en redes).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  C) Estado de prospección (usar la columna 'Estado')</t>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Mercado Libre / El Ferretero (elferretero.com.ar): vendedores del rubro = posibles clientes mayoristas.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Sin contactar  →  Contactado  →  Interesado  →  Cotización enviada  →  Cliente  /  Descartado</t>
-        </is>
-      </c>
+      <c r="B22" s="11" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Filtrá por 'Prioridad = Alta' para empezar por los que tienen web/redes/volumen (compran más).</t>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D) Estado de prospección</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="9" t="inlineStr"/>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Sin contactar → Contactado → Interesado → Cotización enviada → Cliente / Descartado. Filtrá 'Prioridad = Alta' primero.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  D) Regla de oro</t>
-        </is>
-      </c>
+      <c r="B25" s="11" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   No inventar datos. Celda vacía = 'todavía no lo tengo'. Un email o WhatsApp equivocado quema el prospecto y la reputación de la marca.</t>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Regla de oro: no inventar datos. Un mail/WhatsApp equivocado quema el prospecto y la reputación de la marca.</t>
         </is>
       </c>
     </row>
@@ -3024,15 +5075,15 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>UNIPROVEEDORES · Plan Semanal — Redes + Prospección</t>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>UNIPROVEEDORES · Plan Semanal — Redes + Prospección (empezar por el anillo cercano al depósito)</t>
         </is>
       </c>
     </row>
@@ -3044,12 +5095,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Bloque prospección ferreterías</t>
+          <t>Prospección ferreterías</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Contenido / Redes a publicar</t>
+          <t>Contenido / Redes</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -3058,142 +5109,142 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3" ht="58" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Lunes</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Elegí 1 barrio nuevo en Google Maps. Cargá 10 ferreterías nuevas en la hoja 1.</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>IG+FB: foto de producto estrella con precio (cápsula verde). X: oferta corta. WA canal: 'ofertas de la semana'.</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Seguí a 20 ferreterías/proveedores del rubro en IG. Comentá en 5 posteos. Invitá contactos a seguir la Página FB.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Elegí 1 barrio del Anillo 1/2 (empezá pegado al depósito). Cargá 10 ferreterías nuevas (o corré el script de Google Maps).</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>IG+FB: producto estrella con precio (cápsula verde). X: oferta corta. Canal WhatsApp: 'ofertas de la semana'.</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>Seguí 20 ferreterías del rubro en IG. Comentá en 5 posteos. Invitá contactos a seguir la Página FB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Martes</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Llamá/escribí por WhatsApp a 10 ferreterías 'Sin contactar'. Completá Encargado y validá WhatsApp.</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>YouTube: subí 1 Short (review o uso de herramienta, 20-40s, marca de agua). IG Reel = mismo clip.</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>YouTube: respondé todos los comentarios. Pediste sub al final del video. IG: 3 stories con encuesta/pregunta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Escribí por WhatsApp a 10 'Sin contactar' del Anillo 1. Completá Encargado y validá WhatsApp.</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>YouTube: 1 Short (herramienta en acción, 20-40s). Mismo clip → Reel IG.</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>YouTube: respondé todos los comentarios y pedí suscripción. IG: 3 stories con encuesta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Miércoles</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Cargá 10 ferreterías nuevas (otra zona). Pasá a 'Interesado' las que respondieron.</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn: post B2B ('Somos distribuidores mayoristas para ferreterías, envío y garantía'). IG carrusel de catálogo.</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>LinkedIn: conectá con 20 dueños/encargados de ferreterías y comercios. IG: colaborá (collab post) con 1 proveedor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Cargá 10 ferreterías nuevas (Anillo 2). Pasá a 'Interesado' las que respondieron.</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>LinkedIn: post B2B ('mayorista para ferreterías, envío y garantía'). IG: carrusel de catálogo.</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>LinkedIn: conectá con 20 dueños/encargados de ferreterías. IG: collab con 1 proveedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Jueves</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Enviá cotización/lista de precios a los 'Interesados'. Registrá en Notas.</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>IG+FB: testimonio o 'antes/después' con herramienta. WA canal: novedad de stock. X: hilo con 3 tips de uso.</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Concurso simple: 'seguinos + etiquetá a 2 ferreteros' por un descuento. Reglas en story fija.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Enviá lista de precios/cotización a los 'Interesados'. Registrá en Notas.</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>IG+FB: testimonio o 'antes/después'. Canal WhatsApp: novedad de stock. X: hilo con 3 tips.</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>Concurso: 'seguinos + etiquetá a 2 ferreteros' por un descuento. Reglas en story fija.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Viernes</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Seguimiento a todos los contactados de la semana. Cerrá lo que se pueda a 'Cliente'.</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>YouTube: 1 video largo o Short de oferta de fin de semana. Reutilizá para IG/FB/TikTok/X.</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Cross-promo: compartí el video en todas las redes + WA canal. Pediste que lo reenvíen. Fijá el mejor post.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Seguimiento a todos los contactados de la semana. Cerrá lo posible a 'Cliente'.</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>YouTube: video/Short de oferta de fin de semana. Reutilizá para IG/FB/TikTok/X.</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
+          <t>Compartí el video en TODAS las redes + Canal WhatsApp. Fijá el mejor post.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Sáb/Dom</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Actualizá KPIs (nuevos leads, contactados, clientes). Planificá barrio del lunes.</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Programá 2-3 posteos livianos (ofertas, frase de marca). Responder mensajes pendientes.</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Revisá métricas de cada red: qué post creció más → repetí ese formato la semana próxima.</t>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Actualizá KPIs (leads nuevos, contactados, clientes). Planificá el barrio del lunes.</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Programá 2-3 posteos livianos. Respondé mensajes pendientes.</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>Mirá qué post creció más → repetí ese formato la semana próxima.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>META SEMANAL: +30 ferreterías nuevas cargadas · 30 contactadas · 5 clientes nuevos  |  Redes: +50 seguidores por red · 5 publicaciones · 1 video YouTube</t>
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>META SEMANAL: +30 ferreterías nuevas · 30 contactadas · 5 clientes nuevos  |  Redes: +50 seguidores por red · 5 publicaciones · 1 video YouTube</t>
         </is>
       </c>
     </row>
@@ -3217,11 +5268,11 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Cómo crecer en cada red — Uniproveedores</t>
         </is>
@@ -3235,121 +5286,121 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Cómo conseguir seguidores (táctica principal)</t>
+          <t>Táctica principal para sumar seguidores</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Frecuencia ideal + tip clave</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="74" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+          <t>Frecuencia + tip clave</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="72" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>Instagram</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Reels cortos (herramienta en acción, precio en pantalla). Usá 3-5 hashtags locales (#ferreteria #herramientas #caba). Respondé DMs con link de WhatsApp. Collabs con proveedores.</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>1 Reel/día + 3 stories. El Reel con buen gancho en los primeros 2s es lo que más trae seguidores nuevos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="74" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>Reels cortos (herramienta en acción, precio en pantalla). 3-5 hashtags locales (#ferreteria #herramientas #caba). Respondé DMs con link de WhatsApp. Collabs con proveedores.</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>1 Reel/día + 3 stories. El gancho en los primeros 2s es lo que trae seguidores nuevos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="72" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Página (no perfil). Botón 'Enviar WhatsApp'. Publicá ofertas y sumate a grupos de compra/venta y de ferreteros. Invitá a tus contactos a seguir la Página.</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>4-5 posts/semana. Los grupos de FB del rubro son la vía más rápida de alcance B2B gratis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="74" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Página (no perfil), botón 'Enviar WhatsApp'. Sumate a grupos de compra/venta y de ferreteros. Invitá contactos a seguir la Página.</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>4-5 posts/semana. Los grupos del rubro son el alcance B2B gratis más rápido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="72" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Canal WhatsApp</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Creá el Canal desde WhatsApp Business. Poné el link en bio de IG/FB, en la firma de mail y en cada venta. Publicá 'ofertas de la semana' y stock nuevo.</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>2-3 difusiones/semana. Cada cliente que atendés → invitalo al canal. Crece por invitación directa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="74" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Creá el Canal desde WhatsApp Business. Link en bio IG/FB, firma de mail y en cada venta. Publicá 'ofertas de la semana' y stock nuevo.</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>2-3 difusiones/semana. Cada cliente que atendés → invitalo. Crece por invitación directa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="72" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>YouTube</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Shorts (20-40s) reutilizando los Reels + 1 video largo/semana (reviews, 'cómo usar'). Título con palabra clave + miniatura verde de marca. Pedí suscripción al final.</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>2-3 Shorts + 1 largo/semana. Shorts = alcance nuevo; videos largos = autoridad y ventas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="74" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Shorts (20-40s) reutilizando Reels + 1 video largo/semana (reviews, 'cómo usar'). Título con keyword + miniatura verde. Pedí suscripción al final.</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>2-3 Shorts + 1 largo/semana. Shorts = alcance; largos = autoridad y ventas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="72" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>X (Twitter)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Ofertas cortas con imagen, hilos de 'tips de ferretería', responder a cuentas del rubro. Hashtags #Argentina #herramientas.</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>1-2 posts/día. En X crecés respondiendo e interactuando más que publicando solo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="74" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Ofertas cortas con imagen, hilos de tips, responder a cuentas del rubro. #Argentina #herramientas.</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>1-2 posts/día. En X crecés interactuando más que publicando solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="72" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>LinkedIn</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Página de empresa. Postear en tono B2B: 'distribuidor mayorista para ferreterías, envío y garantía'. Conectar con dueños/encargados y comercios. Publicar casos y catálogo.</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>2-3 posts/semana. Es la red para VENDER a ferreterías (no tanto para volumen de seguidores).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>REGLAS QUE APLICAN A TODAS: (1) Mismo @uniproveedoresok y mismo logo en todas. (2) Contenido 1 vez, adaptado a cada red (grabás 1 video → Reel/Short/TikTok/X). (3) Siempre link a WhatsApp wa.me/541135510715. (4) Publicá en horario pico: 12-14h y 19-21h. (5) Respondé TODO comentario/DM el mismo día: el algoritmo premia la interacción.</t>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Página de empresa en tono B2B ('mayorista para ferreterías, envío y garantía'). Conectá con dueños/encargados. Publicá casos y catálogo.</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>2-3 posts/semana. Es la red para VENDERLE a ferreterías, no tanto para volumen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>REGLAS PARA TODAS: (1) Mismo @uniproveedoresok y logo. (2) Grabás 1 video → Reel/Short/TikTok/X. (3) Siempre link a WhatsApp wa.me/541135510715. (4) Horario pico 12-14h y 19-21h. (5) Respondé todo comentario/DM el mismo día.</t>
         </is>
       </c>
     </row>

--- a/data/Ferreterias-CABA-Uniproveedores.xlsx
+++ b/data/Ferreterias-CABA-Uniproveedores.xlsx
@@ -11,6 +11,8 @@
     <sheet name="Cómo completar y escalar" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Plan Semanal Redes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Seguidores por Red" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensajes de contacto" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Tablero y Resultados" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ferreterías CABA'!$A$3:$O$81</definedName>
@@ -22,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,8 +70,16 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -101,6 +111,11 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3F7E6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -128,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -177,6 +192,26 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5411,4 +5446,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="112" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Plantillas de contacto — Anillo 1 (Comuna 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Personalizá lo que está entre [corchetes]. Regla: mensaje corto, valor claro, una sola pregunta y CTA. No mandar catálogo entero en el primer mensaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="11" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1) WhatsApp — primer mensaje (frío)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Hola, ¿cómo va? Te escribo de UNIPROVEEDORES 🛠️, distribuidora mayorista de herramientas y artículos de ferretería. Estamos trabajando con ferreterías de [barrio/zona] con precio mayorista, envío y garantía. ¿Con quién puedo hablar por las compras? Te acerco la lista y las ofertas de la semana, sin compromiso. ¡Gracias!</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2) WhatsApp — seguimiento (48-72 hs después, si no respondió)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1">
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>Hola [nombre]! Te escribí hace unos días de Uniproveedores (mayorista de ferretería). ¿Pudiste ver? Si querés te paso la lista de precios actualizada de esta semana. Si hay algún producto puntual que más vendés, decime cuál y te coto al toque 👍</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3) WhatsApp — con oferta gancho (si sabés qué vende)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="92" customHeight="1">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Hola [nombre]! Esta semana tenemos [producto] a $[precio] mayorista (con envío y garantía). Es de lo que más rota en ferretería. ¿Te preparo una cotización con cantidades para [nombre de la ferretería]?</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4) Email — presentación</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Asunto:  Uniproveedores — precios mayoristas para tu ferretería (envío y garantía)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="92" customHeight="1">
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Hola, ¿cómo estás?
+Soy [tu nombre], de UNIPROVEEDORES, distribuidora mayorista de herramientas y artículos de ferretería. Trabajamos con ferreterías de Capital con precio mayorista, envío y garantía por Mercado Libre.
+Me gustaría acercarte nuestra lista de precios y las ofertas de la semana, sin compromiso. ¿A quién le puedo enviar la información de compras?
+Quedo a disposición.
+[tu nombre] — Uniproveedores
+WhatsApp: 011-3551-0715  ·  ventas@distribuidorauniverso.com
+uniproveedores.com.ar  ·  Mercado Libre: /tienda/uniproveedores</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  5) Guion visita / llamada (para conseguir el nombre del encargado)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="92" customHeight="1">
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>Buenas, ¿el encargado de compras se encuentra? Soy de Uniproveedores, distribuidora mayorista de ferretería. Le quería dejar la lista de precios y ver qué productos le interesan para cotizarle con envío. ¿Con quién tengo el gusto? (→ anotar el nombre en la columna 'Encargado').</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="11" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Tips de cierre:</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Guardá cada número que contactás como contacto → así ven tu foto/estado de empresa y da confianza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Después del primer 'sí', mandá SIEMPRE una cotización concreta con cantidades, no una lista genérica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Invitá a cada contacto a tu Canal de WhatsApp (ofertas) aunque todavía no te compre.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>UNIPROVEEDORES · Tablero de resultados (se actualiza al cargar la columna 'Estado')</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>Embudo de prospección</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Sin contactar</t>
+        </is>
+      </c>
+      <c r="C4" s="21">
+        <f>COUNTIF('Ferreterías CABA'!$M$4:$M$81,"Sin contactar")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Contactado</t>
+        </is>
+      </c>
+      <c r="C5" s="21">
+        <f>COUNTIF('Ferreterías CABA'!$M$4:$M$81,"Contactado")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Interesado</t>
+        </is>
+      </c>
+      <c r="C6" s="21">
+        <f>COUNTIF('Ferreterías CABA'!$M$4:$M$81,"Interesado")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Cotización enviada</t>
+        </is>
+      </c>
+      <c r="C7" s="21">
+        <f>COUNTIF('Ferreterías CABA'!$M$4:$M$81,"Cotización enviada")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="C8" s="21">
+        <f>COUNTIF('Ferreterías CABA'!$M$4:$M$81,"Cliente")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Descartado</t>
+        </is>
+      </c>
+      <c r="C9" s="21">
+        <f>COUNTIF('Ferreterías CABA'!$M$4:$M$81,"Descartado")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>TOTAL en la lista</t>
+        </is>
+      </c>
+      <c r="C10" s="23">
+        <f>COUNTA('Ferreterías CABA'!$M$4:$M$81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Tasa de cierre (Cliente / Contactadas+)</t>
+        </is>
+      </c>
+      <c r="C12" s="25">
+        <f>IFERROR(COUNTIF('Ferreterías CABA'!$M$4:$M$81,"Cliente")/(COUNTA('Ferreterías CABA'!$M$4:$M$81)-COUNTIF('Ferreterías CABA'!$M$4:$M$81,"Sin contactar")-COUNTIF('Ferreterías CABA'!$M$4:$M$81,"")),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Por prioridad</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="C15" s="26">
+        <f>COUNTIF('Ferreterías CABA'!$N$4:$N$81,"Alta")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C16" s="26">
+        <f>COUNTIF('Ferreterías CABA'!$N$4:$N$81,"Media")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="C17" s="26">
+        <f>COUNTIF('Ferreterías CABA'!$N$4:$N$81,"Baja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Por anillo (cercanía al depósito)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Anillo 1</t>
+        </is>
+      </c>
+      <c r="C20" s="26">
+        <f>COUNTIF('Ferreterías CABA'!$B$4:$B$81,"Anillo 1")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Anillo 2</t>
+        </is>
+      </c>
+      <c r="C21" s="26">
+        <f>COUNTIF('Ferreterías CABA'!$B$4:$B$81,"Anillo 2")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Anillo 3</t>
+        </is>
+      </c>
+      <c r="C22" s="26">
+        <f>COUNTIF('Ferreterías CABA'!$B$4:$B$81,"Anillo 3")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>Bitácora semanal (anotá a mano)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Semana</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Contactadas</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Notas / aprendizajes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="27" t="inlineStr">
+        <is>
+          <t>Semana 1</t>
+        </is>
+      </c>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>Semana 2</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="27" t="inlineStr">
+        <is>
+          <t>Semana 3</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="n"/>
+      <c r="D29" s="27" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="27" t="inlineStr">
+        <is>
+          <t>Semana 4</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="n"/>
+      <c r="D30" s="27" t="n"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>Semana 5</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="n"/>
+      <c r="D31" s="27" t="n"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="27" t="inlineStr">
+        <is>
+          <t>Semana 6</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="n"/>
+      <c r="D32" s="27" t="n"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="27" t="inlineStr">
+        <is>
+          <t>Semana 7</t>
+        </is>
+      </c>
+      <c r="C33" s="27" t="n"/>
+      <c r="D33" s="27" t="n"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="27" t="inlineStr">
+        <is>
+          <t>Semana 8</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="n"/>
+      <c r="D34" s="27" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>